--- a/output/roomself_excel/14584.xlsx
+++ b/output/roomself_excel/14584.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37248</v>
+        <v>373108</v>
       </c>
       <c r="D3" t="n">
-        <v>1544</v>
+        <v>7236</v>
       </c>
       <c r="E3" t="n">
-        <v>194</v>
+        <v>780</v>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>683</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>492612</v>
+        <v>98000</v>
       </c>
       <c r="D4" t="n">
-        <v>8788</v>
+        <v>2520</v>
       </c>
       <c r="E4" t="n">
-        <v>1200</v>
+        <v>350</v>
       </c>
       <c r="F4" t="n">
-        <v>981</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>98000</v>
+        <v>137772</v>
       </c>
       <c r="D5" t="n">
-        <v>2520</v>
+        <v>2972</v>
       </c>
       <c r="E5" t="n">
-        <v>350</v>
+        <v>603</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22185</v>
+        <v>37248</v>
       </c>
       <c r="D6" t="n">
-        <v>1192</v>
+        <v>1544</v>
       </c>
       <c r="E6" t="n">
-        <v>618</v>
+        <v>194</v>
       </c>
       <c r="F6" t="n">
-        <v>145</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20502</v>
+        <v>22185</v>
       </c>
       <c r="D7" t="n">
-        <v>1148</v>
+        <v>1192</v>
       </c>
       <c r="E7" t="n">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="F7" t="n">
-        <v>145</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>137772</v>
+        <v>20502</v>
       </c>
       <c r="D8" t="n">
-        <v>2972</v>
+        <v>1148</v>
       </c>
       <c r="E8" t="n">
-        <v>603</v>
+        <v>169</v>
       </c>
       <c r="F8" t="n">
-        <v>356</v>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>119504</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2784</v>
+      </c>
+      <c r="E9" t="n">
+        <v>420</v>
+      </c>
+      <c r="F9" t="n">
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/14584.xlsx
+++ b/output/roomself_excel/14584.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>2696</v>
       </c>
-      <c r="E2" t="n">
-        <v>410</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>333</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>296</v>
+      </c>
+      <c r="J2" t="n">
+        <v>32</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +551,38 @@
       <c r="D3" t="n">
         <v>7236</v>
       </c>
-      <c r="E3" t="n">
-        <v>780</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>683</v>
+        <v>540</v>
+      </c>
+      <c r="G3" t="n">
+        <v>37</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>407</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>177</v>
+      </c>
+      <c r="M3" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +600,23 @@
       <c r="D4" t="n">
         <v>2520</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>350</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>30</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +633,38 @@
       <c r="D5" t="n">
         <v>2972</v>
       </c>
-      <c r="E5" t="n">
-        <v>603</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
         <v>356</v>
+      </c>
+      <c r="G5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>211</v>
+      </c>
+      <c r="J5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>387</v>
+      </c>
+      <c r="M5" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +682,23 @@
       <c r="D6" t="n">
         <v>1544</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>194</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>37</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +715,23 @@
       <c r="D7" t="n">
         <v>1192</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>135</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>21</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +748,31 @@
       <c r="D8" t="n">
         <v>1148</v>
       </c>
-      <c r="E8" t="n">
-        <v>169</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>145</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="G8" t="n">
+        <v>21</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>148</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +789,31 @@
       <c r="D9" t="n">
         <v>2784</v>
       </c>
-      <c r="E9" t="n">
-        <v>420</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>329</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="G9" t="n">
+        <v>32</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>388</v>
+      </c>
+      <c r="J9" t="n">
+        <v>21</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
